--- a/Day03/배포용/비전공/03_3일차_팀프로젝트_실습기획서_작성예제.xlsx
+++ b/Day03/배포용/비전공/03_3일차_팀프로젝트_실습기획서_작성예제.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\ai-onboarding\Day03\공통\프로젝트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edwin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEC8E8C-9F80-44D9-B0E7-7352AF5DF5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178D16F1-7C00-4B23-AC55-733BDF6F5FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7590" yWindow="1545" windowWidth="23160" windowHeight="16500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="246">
   <si>
     <t>실습 소재</t>
   </si>
@@ -419,18 +419,6 @@
   </si>
   <si>
     <t>선정하지 않은 나머지 4개 권역 데이터 및 기능</t>
-  </si>
-  <si>
-    <t>리스크 및 대응</t>
-  </si>
-  <si>
-    <t>Kakao Maps API 키 발급 지연 - Day 1에 미리 신청해 개발 병목 방지</t>
-  </si>
-  <si>
-    <t>지도 마커 데이터량 과다 시 로딩 지연 - 권역 내 데이터 개수 사전 확인 후 페이징/클러스터링 검토</t>
-  </si>
-  <si>
-    <t>신입 개발자의 지도 API 학습곡선 - 공식 문서.예제 코드를 착수 전 미리 확보해 공유</t>
   </si>
   <si>
     <t>LocalHub WBS + 간트차트 (Day 1~Day 3 기준 예시)</t>
@@ -4862,361 +4850,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>결과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시각화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>순위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>축제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>캘린더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>날씨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>연동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>예비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발기간</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>완성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가능성을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최우선으로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>판단</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="맑은 고딕"/>
@@ -6155,10 +5788,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>이 프로젝트의 MVP 범위를 MoSCoW 방식으로 정리해줘._x000B_Must have는 개발 의뢰 문서(RFP)의 '필수' 항목 그대로, _x000B_Should/Could have는 평과 결과를 고려,Won't have(이번엔 안 하는 것)도 명확히 구분해서 표로 만들어줘._x000B_--- (개발 의뢰 문서(RFP) 원문 전체 및 평가 결과 넣기) ---</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7276,6 +6905,570 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="1"/>
+      </rPr>
+      <t>④</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> WBS(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작업분해구조</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>①</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>요구사항분석</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>②</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>아이디어도출</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나머지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선택기능</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 프로젝트의 MVP 범위를 MoSCoW 방식으로 정리해줘._x000B_Must have는 개발 의뢰 문서(RFP)의 '필수' 항목 그대로, Should/Could have는 평가 결과를 고려,Won't have(이번엔 안 하는 것)도 명확히 구분해서 표로 만들어줘.--- (개발 의뢰 문서(RFP) 원문 전체 및 평가 결과 넣기) ---</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시각화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>축제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캘린더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날씨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>연동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예비</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) 
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최우선으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="맑은 고딕"/>
@@ -7855,197 +8048,102 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">
---- (선택 가능한 후보 표 붙여넣기, 9 page 내용 ) ---</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="1"/>
-      </rPr>
-      <t>④</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> WBS(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작업분해구조</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>①</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>요구사항분석</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>②</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>아이디어도출</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선정하지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>나머지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>선택기능</t>
+--- (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붙여넣기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ) ---</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -8057,7 +8155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;Day &quot;0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8301,6 +8399,20 @@
       <name val="Arial"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -8452,7 +8564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8463,7 +8575,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8485,9 +8596,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8531,25 +8639,43 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8568,6 +8694,33 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -8585,24 +8738,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8896,24 +9031,24 @@
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
       <c r="B2" s="30" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C2" s="30"/>
     </row>
     <row r="4" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B4" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>218</v>
+      <c r="B4" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36.950000000000003" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>221</v>
+      <c r="C5" s="22" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="20.65" customHeight="1">
@@ -8921,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="19.5" customHeight="1">
@@ -8929,33 +9064,33 @@
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="28.7" customHeight="1">
       <c r="B9" s="35" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C9" s="36"/>
     </row>
     <row r="10" spans="2:3" ht="40.5">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>224</v>
+      <c r="C10" s="22" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="40.5">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>226</v>
+      <c r="C11" s="22" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -8963,7 +9098,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -8971,7 +9106,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -8979,22 +9114,22 @@
       </c>
     </row>
     <row r="15" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>227</v>
+      <c r="C15" s="22" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="52"/>
+      <c r="C17" s="38"/>
     </row>
     <row r="18" spans="2:3" ht="33.950000000000003" customHeight="1">
       <c r="B18" s="31" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C18" s="32"/>
     </row>
@@ -9030,154 +9165,155 @@
   <sheetPr>
     <tabColor rgb="FF1E2761"/>
   </sheetPr>
-  <dimension ref="B2:F17"/>
+  <dimension ref="B2:F13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="57.140625" customWidth="1"/>
+    <col min="4" max="4" width="70.7109375" customWidth="1"/>
     <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" customWidth="1"/>
+    <col min="9" max="9" width="98" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B5" s="53" t="s">
-        <v>246</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="E5" s="55" t="s">
+      <c r="D5" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="129.75" customHeight="1">
+      <c r="B6" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="129.75" customHeight="1">
+      <c r="B7" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B6" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B7" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="129.75" customHeight="1">
-      <c r="B8" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:6" ht="15" customHeight="1">
-      <c r="B10" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
+      <c r="B10" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
       <c r="F10" s="36"/>
     </row>
     <row r="11" spans="2:6" ht="24" customHeight="1">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
+      <c r="C11" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="2:6" ht="24" customHeight="1">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
+      <c r="C12" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="2:6" ht="24" customHeight="1">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-    </row>
-    <row r="17" customFormat="1"/>
+      <c r="C13" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="C13:F13"/>
@@ -9209,68 +9345,68 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
+      <c r="B3" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="36"/>
     </row>
     <row r="4" spans="2:6" ht="33.75" customHeight="1">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>243</v>
+      <c r="F6" s="22" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -9278,16 +9414,16 @@
       </c>
     </row>
     <row r="8" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>50</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -9295,16 +9431,16 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -9312,16 +9448,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -9329,16 +9465,16 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -9346,16 +9482,16 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -9363,16 +9499,16 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -9380,16 +9516,16 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>76</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -9397,16 +9533,16 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="45.75" customHeight="1">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
@@ -9441,258 +9577,260 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="2:8" ht="63.4" customHeight="1">
-      <c r="B3" s="44" t="s">
-        <v>235</v>
-      </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
       <c r="H3" s="36"/>
     </row>
     <row r="4" spans="2:8" ht="31.5" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>91</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>3</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>5</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>5</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f t="shared" ref="G5:G12" si="0">IF(OR(E5="",F5=""),"",E5*F5*2)</f>
         <v>50</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>3</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>3</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>3</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>2</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>4</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>3</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>4</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>2</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>3</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>2</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>5</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>2</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>4</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>2</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>4</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>106</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>3</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>3</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>2</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>2</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>4</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>2</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="118.7" customHeight="1">
-      <c r="B14" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="36"/>
+      <c r="B14" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B14:H14"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C14:H14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="G5:G12">
@@ -9710,7 +9848,7 @@
   <sheetPr>
     <tabColor rgb="FF028090"/>
   </sheetPr>
-  <dimension ref="B2:C29"/>
+  <dimension ref="B2:C24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -9720,13 +9858,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="40"/>
+      <c r="C2" s="42"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="45" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="36"/>
@@ -9735,8 +9873,8 @@
       <c r="B4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>237</v>
+      <c r="C4" s="22" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1">
@@ -9764,10 +9902,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="12"/>
+      <c r="C9" s="55"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
       <c r="B10" s="33" t="s">
@@ -9783,7 +9921,7 @@
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
       <c r="B12" s="31" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C12" s="32"/>
     </row>
@@ -9800,10 +9938,10 @@
       <c r="C14" s="34"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="13"/>
+      <c r="C16" s="53"/>
     </row>
     <row r="17" spans="2:3" ht="25.5" customHeight="1">
       <c r="B17" s="33" t="s">
@@ -9824,10 +9962,10 @@
       <c r="C19" s="34"/>
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="14"/>
+      <c r="C21" s="51"/>
     </row>
     <row r="22" spans="2:3" ht="25.5" customHeight="1">
       <c r="B22" s="33" t="s">
@@ -9842,34 +9980,10 @@
       <c r="C23" s="34"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="56" t="s">
-        <v>248</v>
+      <c r="B24" s="39" t="s">
+        <v>241</v>
       </c>
       <c r="C24" s="34"/>
-    </row>
-    <row r="26" spans="2:3" ht="15" customHeight="1">
-      <c r="B26" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="4"/>
-    </row>
-    <row r="27" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B27" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="32"/>
-    </row>
-    <row r="28" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B28" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="34"/>
-    </row>
-    <row r="29" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B29" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -9878,17 +9992,17 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9918,580 +10032,580 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+    </row>
+    <row r="3" spans="2:13" ht="69" customHeight="1">
+      <c r="B3" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="58"/>
+    </row>
+    <row r="4" spans="2:13" ht="25.5" customHeight="1">
+      <c r="B4" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-    </row>
-    <row r="3" spans="2:13" ht="69" customHeight="1">
-      <c r="B3" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="47"/>
-    </row>
-    <row r="4" spans="2:13" ht="25.5" customHeight="1">
-      <c r="B4" s="15" t="s">
+      <c r="F4" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="K4" s="12">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <v>2</v>
+      </c>
+      <c r="M4" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="42" customHeight="1">
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="D5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K4" s="16">
+      <c r="F5" s="25">
         <v>1</v>
       </c>
-      <c r="L4" s="16">
-        <v>2</v>
-      </c>
-      <c r="M4" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" ht="42" customHeight="1">
-      <c r="B5" s="10">
+      <c r="G5" s="25">
         <v>1</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="29">
-        <v>1</v>
-      </c>
-      <c r="G5" s="29">
-        <v>1</v>
-      </c>
-      <c r="H5" s="10">
+      <c r="H5" s="9">
         <f t="shared" ref="H5:H18" si="0">G5-F5+1</f>
         <v>1</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="9">
         <v>0</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>148</v>
+      <c r="J5" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="2:13" ht="42" customHeight="1">
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="29">
+      <c r="E6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="25">
         <v>1</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="25">
         <v>1</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>0</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>148</v>
+      <c r="J6" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
     <row r="7" spans="2:13" ht="42" customHeight="1">
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>3</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>151</v>
+      <c r="C7" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F7" s="29">
+        <v>148</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="25">
         <v>1</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="25">
         <v>1</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>0</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>148</v>
+      <c r="J7" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
     <row r="8" spans="2:13" ht="42" customHeight="1">
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>4</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>151</v>
+      <c r="C8" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="29">
+        <v>150</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="25">
         <v>1</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="25">
         <v>1</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>0</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>148</v>
+      <c r="J8" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="2:13" ht="42" customHeight="1">
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>155</v>
+      <c r="C9" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F9" s="29">
+        <v>152</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="25">
         <v>2</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="25">
         <v>2</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>0</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>148</v>
+      <c r="J9" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="2:13" ht="42" customHeight="1">
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>155</v>
+      <c r="C10" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F10" s="29">
+        <v>154</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="25">
         <v>2</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="25">
         <v>2</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>0</v>
       </c>
-      <c r="J10" s="10" t="s">
-        <v>148</v>
+      <c r="J10" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="42" customHeight="1">
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>7</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="F11" s="29">
+      <c r="E11" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="25">
         <v>2</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="25">
         <v>2</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <v>0</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>148</v>
+      <c r="J11" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="42" customHeight="1">
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>8</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>155</v>
+      <c r="C12" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="29">
+        <v>156</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="25">
         <v>2</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="25">
         <v>2</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>0</v>
       </c>
-      <c r="J12" s="10" t="s">
-        <v>148</v>
+      <c r="J12" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:13" ht="42" customHeight="1">
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>9</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>155</v>
+      <c r="C13" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F13" s="29">
+      <c r="E13" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="25">
         <v>2</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="25">
         <v>2</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <v>0</v>
       </c>
-      <c r="J13" s="10" t="s">
-        <v>148</v>
+      <c r="J13" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:13" ht="42" customHeight="1">
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>10</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>155</v>
+      <c r="C14" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F14" s="29">
+        <v>158</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="25">
         <v>2</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="25">
         <v>2</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>0</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>148</v>
+      <c r="J14" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:13" ht="42" customHeight="1">
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>164</v>
+      <c r="C15" s="16" t="s">
+        <v>160</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F15" s="29">
+        <v>161</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="25">
         <v>3</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="25">
         <v>3</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="9">
         <v>0</v>
       </c>
-      <c r="J15" s="10" t="s">
-        <v>148</v>
+      <c r="J15" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="2:13" ht="42" customHeight="1">
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>166</v>
+      <c r="C16" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="29">
+        <v>163</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F16" s="25">
         <v>3</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="25">
         <v>3</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="9">
         <v>0</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>148</v>
+      <c r="J16" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
     <row r="17" spans="2:13" ht="42" customHeight="1">
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>168</v>
+      <c r="C17" s="18" t="s">
+        <v>164</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" s="29">
+        <v>165</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="25">
         <v>3</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="25">
         <v>3</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>0</v>
       </c>
-      <c r="J17" s="10" t="s">
-        <v>148</v>
+      <c r="J17" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
     <row r="18" spans="2:13" ht="42" customHeight="1">
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>14</v>
       </c>
-      <c r="C18" s="23" t="s">
-        <v>170</v>
+      <c r="C18" s="19" t="s">
+        <v>166</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" s="29">
+        <v>167</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="25">
         <v>3</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="25">
         <v>3</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>0</v>
       </c>
-      <c r="J18" s="10" t="s">
-        <v>148</v>
+      <c r="J18" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="24" t="s">
-        <v>172</v>
+      <c r="B20" s="20" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="17" t="s">
-        <v>145</v>
+      <c r="B21" s="13" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="15" customHeight="1">
+      <c r="B23" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="19" t="s">
-        <v>155</v>
-      </c>
-    </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="15" customHeight="1">
+      <c r="B25" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="15" customHeight="1">
+      <c r="B26" s="18" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="21" t="s">
+    <row r="27" spans="2:13" ht="15" customHeight="1">
+      <c r="B27" s="19" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="22" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="23" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="25" t="s">
-        <v>173</v>
+      <c r="B28" s="21" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -10524,183 +10638,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="42"/>
+    </row>
+    <row r="3" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B3" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="36"/>
+    </row>
+    <row r="5" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B5" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="30" customHeight="1">
+      <c r="B6" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="40"/>
-    </row>
-    <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="50" t="s">
+      <c r="C6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="36"/>
-    </row>
-    <row r="5" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="7" spans="2:3" ht="30" customHeight="1">
+      <c r="B7" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="30" customHeight="1">
-      <c r="B6" s="5" t="s">
+    <row r="8" spans="2:3" ht="30" customHeight="1">
+      <c r="B8" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="30" customHeight="1">
-      <c r="B7" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="30" customHeight="1">
-      <c r="B8" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1">
       <c r="B9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="30" customHeight="1">
+      <c r="B10" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="30" customHeight="1">
+      <c r="B11" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="30" customHeight="1">
-      <c r="B10" s="5" t="s">
+    <row r="12" spans="2:3" ht="30" customHeight="1">
+      <c r="B12" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="30" customHeight="1">
-      <c r="B11" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="30" customHeight="1">
-      <c r="B12" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="30" customHeight="1">
       <c r="B13" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30" customHeight="1">
-      <c r="B14" s="5" t="s">
-        <v>194</v>
+      <c r="B14" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="30" customHeight="1">
       <c r="B15" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="30" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30" customHeight="1">
-      <c r="B17" s="5" t="s">
-        <v>200</v>
+      <c r="B17" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1">
       <c r="B18" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30" customHeight="1">
       <c r="B19" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="30" customHeight="1">
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="30" customHeight="1">
       <c r="B21" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="30" customHeight="1">
       <c r="B22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="30" customHeight="1">
+      <c r="B23" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="30" customHeight="1">
+      <c r="B24" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1">
-      <c r="B23" s="5" t="s">
+    <row r="25" spans="2:3" ht="30" customHeight="1">
+      <c r="B25" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1">
-      <c r="B24" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1">
-      <c r="B25" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
